--- a/sources/table_normalization/xlsx/economy-table102.xlsx
+++ b/sources/table_normalization/xlsx/economy-table102.xlsx
@@ -362,7 +362,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -378,12 +378,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,7 +459,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -511,26 +505,23 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1381,7 +1372,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1498,7 +1489,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="12.5" customHeight="1">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="8">
@@ -1536,20 +1527,20 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="19.399999999999999" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="9" t="s">
@@ -1743,20 +1734,20 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="19.399999999999999" customHeight="1">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="9" t="s">
@@ -1912,20 +1903,20 @@
       </c>
     </row>
     <row r="19" spans="1:14" ht="19.399999999999999" customHeight="1">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="9" t="s">
@@ -2272,20 +2263,20 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="19.399999999999999" customHeight="1">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="9" t="s">
@@ -2554,20 +2545,20 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="31.4" customHeight="1">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="9" t="s">
@@ -2646,20 +2637,20 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="19.399999999999999" customHeight="1">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="9" t="s">
@@ -3624,8 +3615,8 @@
       <c r="G68" s="16"/>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="29"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="24"/>
       <c r="L68" s="18"/>
     </row>
     <row r="71" spans="1:15" ht="27.75" customHeight="1"/>
@@ -3643,8 +3634,8 @@
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="16"/>
-      <c r="N79" s="28"/>
-      <c r="O79" s="29"/>
+      <c r="N79" s="23"/>
+      <c r="O79" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
